--- a/data/trans_dic/P37-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P37-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se ha vacunado de la gripe en la última campaña</t>
+          <t>Población que se ha vacunado de la gripe en la última campaña (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,59; 17,14</t>
+          <t>10,29; 16,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,01; 19,37</t>
+          <t>11,76; 19,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,61; 19,04</t>
+          <t>11,89; 19,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33,36; 41,65</t>
+          <t>33,74; 42,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,77; 16,13</t>
+          <t>9,07; 16,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,3; 15,73</t>
+          <t>8,13; 16,12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,68; 17,39</t>
+          <t>9,6; 17,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>32,65; 40,22</t>
+          <t>32,79; 40,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,71; 15,4</t>
+          <t>10,74; 15,45</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,1; 16,68</t>
+          <t>11,11; 16,25</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,84; 17,14</t>
+          <t>11,8; 17,15</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>34,21; 40,2</t>
+          <t>34,48; 40,45</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,4; 20,43</t>
+          <t>12,33; 20,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,86; 23,66</t>
+          <t>15,32; 23,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,1; 17,12</t>
+          <t>10,06; 17,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32,83; 41,47</t>
+          <t>32,84; 42,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,72; 10,27</t>
+          <t>4,62; 9,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,55; 13,73</t>
+          <t>6,48; 13,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,25; 12,39</t>
+          <t>6,17; 12,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>26,77; 34,57</t>
+          <t>26,69; 34,45</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,35; 13,85</t>
+          <t>9,31; 13,93</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,88; 17,47</t>
+          <t>12,02; 17,7</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,01; 13,99</t>
+          <t>9,0; 13,67</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>31,02; 37,0</t>
+          <t>31,0; 37,15</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,81; 15,3</t>
+          <t>9,86; 15,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,77; 21,44</t>
+          <t>14,82; 21,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,25; 20,5</t>
+          <t>13,85; 20,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,52; 33,33</t>
+          <t>8,4; 33,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,23; 18,62</t>
+          <t>8,43; 18,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,73; 17,33</t>
+          <t>8,25; 16,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,6; 24,64</t>
+          <t>11,78; 23,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>33,88; 45,83</t>
+          <t>33,63; 45,37</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,22; 15,11</t>
+          <t>10,33; 15,23</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13,75; 18,91</t>
+          <t>13,67; 19,06</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14,54; 20,47</t>
+          <t>14,58; 20,24</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,99; 35,17</t>
+          <t>10,82; 34,97</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,6; 18,74</t>
+          <t>14,51; 18,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,5; 22,14</t>
+          <t>17,37; 22,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,05; 19,4</t>
+          <t>14,95; 19,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30,55; 36,52</t>
+          <t>30,43; 36,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,65; 15,55</t>
+          <t>10,59; 15,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,83; 14,51</t>
+          <t>9,9; 15,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,05; 14,65</t>
+          <t>10,25; 15,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>29,94; 72,08</t>
+          <t>30,02; 66,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,72; 17,07</t>
+          <t>13,59; 16,67</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15,07; 18,42</t>
+          <t>14,95; 18,48</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13,56; 16,78</t>
+          <t>13,53; 16,73</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>31,65; 56,57</t>
+          <t>31,66; 57,34</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,37; 18,47</t>
+          <t>10,99; 18,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,16; 22,09</t>
+          <t>15,18; 21,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,32; 21,67</t>
+          <t>15,61; 21,76</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23,35; 31,36</t>
+          <t>23,06; 31,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,24; 17,19</t>
+          <t>11,16; 17,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,03; 22,67</t>
+          <t>16,93; 22,73</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,95; 19,59</t>
+          <t>13,96; 19,69</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>23,7; 36,35</t>
+          <t>23,77; 36,42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12,06; 16,78</t>
+          <t>12,05; 17,02</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17,15; 21,61</t>
+          <t>17,16; 21,43</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15,61; 19,67</t>
+          <t>15,48; 19,51</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>24,39; 33,06</t>
+          <t>23,42; 32,98</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,28; 6,79</t>
+          <t>2,22; 6,79</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,42; 12,98</t>
+          <t>5,39; 12,83</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,4; 9,44</t>
+          <t>3,62; 9,44</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,77; 10,99</t>
+          <t>2,71; 11,2</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19,94; 24,69</t>
+          <t>19,87; 24,51</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,73; 30,31</t>
+          <t>24,84; 30,41</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,49; 28,06</t>
+          <t>22,52; 28,14</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>42,49; 49,33</t>
+          <t>43,04; 49,22</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16,71; 20,68</t>
+          <t>16,77; 20,69</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>21,56; 26,08</t>
+          <t>21,3; 25,97</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>18,78; 23,59</t>
+          <t>19,01; 23,54</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>33,27; 39,34</t>
+          <t>32,9; 39,1</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>12,73; 15,1</t>
+          <t>12,76; 15,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,35; 19,07</t>
+          <t>16,41; 18,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14,51; 16,94</t>
+          <t>14,65; 17,05</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22,72; 31,94</t>
+          <t>23,15; 31,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>14,69; 17,22</t>
+          <t>14,7; 17,06</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,92; 19,65</t>
+          <t>16,93; 19,62</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,82; 18,51</t>
+          <t>15,85; 18,57</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>34,79; 50,6</t>
+          <t>35,03; 52,58</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14,04; 15,69</t>
+          <t>14,05; 15,74</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16,92; 18,89</t>
+          <t>16,98; 18,88</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15,56; 17,34</t>
+          <t>15,58; 17,43</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>30,98; 40,62</t>
+          <t>30,91; 40,73</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se ha vacunado de la gripe en la última campaña</t>
+          <t>Población que se ha vacunado de la gripe en la última campaña (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>50172; 81192</t>
+          <t>48749; 80390</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>52396; 84474</t>
+          <t>51277; 82999</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>49818; 81700</t>
+          <t>51039; 81710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>168547; 210397</t>
+          <t>170456; 215108</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>26909; 49454</t>
+          <t>27831; 50897</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26091; 49455</t>
+          <t>25558; 50685</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33593; 60356</t>
+          <t>33318; 62272</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>146112; 179960</t>
+          <t>146712; 181851</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>83557; 120207</t>
+          <t>83825; 120575</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>83344; 125240</t>
+          <t>83412; 121951</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>91926; 132997</t>
+          <t>91576; 133082</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>325916; 382984</t>
+          <t>328519; 385345</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>45499; 74953</t>
+          <t>45241; 73534</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>62227; 99107</t>
+          <t>64167; 98965</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38096; 64591</t>
+          <t>37952; 64659</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>148445; 187514</t>
+          <t>148493; 190195</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17512; 38098</t>
+          <t>17143; 36967</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22062; 46256</t>
+          <t>21823; 44812</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23254; 46118</t>
+          <t>22955; 45608</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>102434; 132244</t>
+          <t>102128; 131812</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>68951; 102195</t>
+          <t>68679; 102810</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>89777; 132047</t>
+          <t>90860; 133789</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>67510; 104861</t>
+          <t>67424; 102478</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>258971; 308899</t>
+          <t>258785; 310145</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>53233; 82979</t>
+          <t>53496; 83106</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>92816; 134704</t>
+          <t>93124; 133508</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>74377; 106989</t>
+          <t>72285; 108172</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>50268; 222763</t>
+          <t>56111; 224603</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>13810; 31240</t>
+          <t>14136; 31206</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22709; 45073</t>
+          <t>21452; 42895</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19270; 40928</t>
+          <t>19564; 39665</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>56553; 76502</t>
+          <t>56135; 75731</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>72545; 107335</t>
+          <t>73368; 108157</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>122173; 168040</t>
+          <t>121465; 169319</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>100020; 140869</t>
+          <t>100339; 139288</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>83444; 293728</t>
+          <t>90331; 292084</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>180794; 232023</t>
+          <t>179743; 230559</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>202852; 256610</t>
+          <t>201305; 257694</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>172981; 223003</t>
+          <t>171870; 222817</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>316102; 377880</t>
+          <t>314864; 378911</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>76080; 111088</t>
+          <t>75621; 111944</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>75336; 111263</t>
+          <t>75929; 115640</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>82999; 120972</t>
+          <t>84632; 124049</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>292837; 705024</t>
+          <t>293659; 654919</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>267968; 333400</t>
+          <t>265418; 325594</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>290195; 354751</t>
+          <t>287949; 355920</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>267814; 331475</t>
+          <t>267315; 330557</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>637141; 1138797</t>
+          <t>637342; 1154243</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>36259; 64593</t>
+          <t>38433; 64893</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>77239; 112538</t>
+          <t>77341; 111734</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>95099; 134533</t>
+          <t>96911; 135082</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>110902; 148983</t>
+          <t>109552; 147834</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>63924; 97776</t>
+          <t>63475; 99595</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>129664; 172610</t>
+          <t>128932; 173064</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>103010; 144645</t>
+          <t>103083; 145380</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>198802; 304974</t>
+          <t>199457; 305586</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>110801; 154077</t>
+          <t>110656; 156324</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>218011; 274640</t>
+          <t>218068; 272428</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>212135; 267301</t>
+          <t>210379; 265194</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>320440; 434482</t>
+          <t>307689; 433357</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6769; 20177</t>
+          <t>6596; 20180</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>14357; 34394</t>
+          <t>14292; 33996</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9777; 27099</t>
+          <t>10398; 27109</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6667; 26427</t>
+          <t>6512; 26946</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>248759; 308031</t>
+          <t>247947; 305879</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>274370; 336230</t>
+          <t>275608; 337332</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>243337; 303640</t>
+          <t>243726; 304513</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>323534; 375573</t>
+          <t>327708; 374763</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>258131; 319479</t>
+          <t>259153; 319758</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>296345; 358440</t>
+          <t>292696; 356889</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257198; 322969</t>
+          <t>260345; 322355</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>333317; 394159</t>
+          <t>329664; 391740</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>416200; 493455</t>
+          <t>417111; 493850</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>558810; 651477</t>
+          <t>560676; 646853</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>491185; 573598</t>
+          <t>495989; 577202</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>766921; 1078157</t>
+          <t>781514; 1071862</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>496126; 581322</t>
+          <t>496309; 575906</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>600523; 697359</t>
+          <t>600878; 696172</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>558653; 653862</t>
+          <t>559667; 655704</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1243874; 1809090</t>
+          <t>1252539; 1879841</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>932910; 1042821</t>
+          <t>933432; 1046199</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1178917; 1315924</t>
+          <t>1182665; 1315438</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1076405; 1199428</t>
+          <t>1077897; 1205914</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2153703; 2823420</t>
+          <t>2149000; 2831238</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P37-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P37-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,1%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,29; 16,97</t>
+          <t>10,53; 17,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,76; 19,03</t>
+          <t>11,89; 19,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,89; 19,04</t>
+          <t>11,62; 19,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33,74; 42,58</t>
+          <t>33,49; 41,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,07; 16,6</t>
+          <t>8,76; 16,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,13; 16,12</t>
+          <t>8,52; 16,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,6; 17,94</t>
+          <t>9,67; 17,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>32,79; 40,64</t>
+          <t>32,59; 40,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,74; 15,45</t>
+          <t>10,79; 15,58</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,11; 16,25</t>
+          <t>11,18; 16,53</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,8; 17,15</t>
+          <t>11,71; 17,12</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>34,48; 40,45</t>
+          <t>34,45; 39,9</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>34,04%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,33; 20,04</t>
+          <t>12,47; 20,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,32; 23,63</t>
+          <t>14,33; 23,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,06; 17,14</t>
+          <t>10,24; 17,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32,84; 42,06</t>
+          <t>32,57; 41,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,62; 9,97</t>
+          <t>4,64; 10,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,48; 13,3</t>
+          <t>6,47; 13,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,17; 12,25</t>
+          <t>6,32; 11,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>26,69; 34,45</t>
+          <t>26,52; 34,32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,31; 13,93</t>
+          <t>9,3; 14,28</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12,02; 17,7</t>
+          <t>12,03; 18,15</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,0; 13,67</t>
+          <t>9,09; 13,8</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>31,0; 37,15</t>
+          <t>31,11; 37,15</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>33,66%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,86; 15,32</t>
+          <t>10,04; 15,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,82; 21,25</t>
+          <t>14,88; 21,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,85; 20,73</t>
+          <t>14,21; 20,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,4; 33,61</t>
+          <t>27,45; 35,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,43; 18,6</t>
+          <t>7,63; 18,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,25; 16,49</t>
+          <t>8,44; 17,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,78; 23,88</t>
+          <t>11,72; 25,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>33,63; 45,37</t>
+          <t>33,24; 44,35</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,33; 15,23</t>
+          <t>10,39; 15,21</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13,67; 19,06</t>
+          <t>13,63; 18,72</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14,58; 20,24</t>
+          <t>14,41; 20,23</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,82; 34,97</t>
+          <t>30,14; 36,92</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>32,07%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,51; 18,62</t>
+          <t>14,46; 18,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,37; 22,23</t>
+          <t>17,4; 22,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,95; 19,38</t>
+          <t>14,94; 19,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30,43; 36,62</t>
+          <t>30,71; 36,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,59; 15,67</t>
+          <t>10,63; 15,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,9; 15,08</t>
+          <t>9,96; 14,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,25; 15,02</t>
+          <t>10,31; 15,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>30,02; 66,96</t>
+          <t>27,55; 32,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,59; 16,67</t>
+          <t>13,71; 16,97</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14,95; 18,48</t>
+          <t>15,02; 18,37</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13,53; 16,73</t>
+          <t>13,59; 16,65</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>31,66; 57,34</t>
+          <t>30,05; 34,0</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>31,04%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,99; 18,56</t>
+          <t>10,83; 18,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,18; 21,93</t>
+          <t>14,98; 21,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,61; 21,76</t>
+          <t>15,65; 21,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23,06; 31,12</t>
+          <t>21,33; 27,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,16; 17,51</t>
+          <t>11,4; 17,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,93; 22,73</t>
+          <t>16,85; 22,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,96; 19,69</t>
+          <t>14,18; 19,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>23,77; 36,42</t>
+          <t>32,75; 38,09</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12,05; 17,02</t>
+          <t>11,92; 16,56</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17,16; 21,43</t>
+          <t>17,19; 21,39</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15,48; 19,51</t>
+          <t>15,39; 19,56</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>23,42; 32,98</t>
+          <t>28,7; 33,38</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>36,15%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,22; 6,79</t>
+          <t>2,04; 6,76</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,39; 12,83</t>
+          <t>5,35; 12,73</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,62; 9,44</t>
+          <t>3,39; 9,9</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,71; 11,2</t>
+          <t>2,69; 9,72</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19,87; 24,51</t>
+          <t>19,88; 24,6</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,84; 30,41</t>
+          <t>24,61; 30,07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,52; 28,14</t>
+          <t>22,57; 28,06</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>43,04; 49,22</t>
+          <t>41,96; 48,37</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16,77; 20,69</t>
+          <t>16,72; 20,67</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>21,3; 25,97</t>
+          <t>21,49; 26,11</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>19,01; 23,54</t>
+          <t>18,97; 23,66</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>32,9; 39,1</t>
+          <t>33,01; 39,02</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>33,63%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>12,76; 15,11</t>
+          <t>12,83; 15,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,41; 18,93</t>
+          <t>16,33; 19,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14,65; 17,05</t>
+          <t>14,36; 17,07</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23,15; 31,75</t>
+          <t>29,43; 32,57</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>14,7; 17,06</t>
+          <t>14,65; 17,11</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,93; 19,62</t>
+          <t>16,86; 19,69</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,85; 18,57</t>
+          <t>15,98; 18,71</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>35,03; 52,58</t>
+          <t>34,82; 37,49</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14,05; 15,74</t>
+          <t>14,04; 15,79</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16,98; 18,88</t>
+          <t>17,02; 18,92</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15,58; 17,43</t>
+          <t>15,65; 17,5</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>30,91; 40,73</t>
+          <t>32,61; 34,66</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>191081</t>
+          <t>207134</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>162997</t>
+          <t>178300</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>354078</t>
+          <t>385435</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>48749; 80390</t>
+          <t>49868; 80529</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>51277; 82999</t>
+          <t>51858; 83578</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>51039; 81710</t>
+          <t>49866; 81816</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>170456; 215108</t>
+          <t>184411; 228628</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>27831; 50897</t>
+          <t>26869; 49817</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25558; 50685</t>
+          <t>26783; 50640</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33318; 62272</t>
+          <t>33559; 60569</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>146712; 181851</t>
+          <t>159190; 196816</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>83825; 120575</t>
+          <t>84219; 121575</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>83412; 121951</t>
+          <t>83903; 124115</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>91576; 133082</t>
+          <t>90867; 132897</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>328519; 385345</t>
+          <t>357915; 414574</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>167865</t>
+          <t>180264</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>116029</t>
+          <t>128253</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>283895</t>
+          <t>308517</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>45241; 73534</t>
+          <t>45743; 74984</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>64167; 98965</t>
+          <t>60007; 97407</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37952; 64659</t>
+          <t>38627; 66182</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>148493; 190195</t>
+          <t>157391; 201747</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17143; 36967</t>
+          <t>17212; 37872</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21823; 44812</t>
+          <t>21794; 45102</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22955; 45608</t>
+          <t>23532; 44347</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>102128; 131812</t>
+          <t>112213; 145208</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>68679; 102810</t>
+          <t>68634; 105368</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>90860; 133789</t>
+          <t>90898; 137130</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>67424; 102478</t>
+          <t>68138; 103467</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>258785; 310145</t>
+          <t>281995; 336740</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>136014</t>
+          <t>149008</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>65771</t>
+          <t>72858</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>201785</t>
+          <t>221866</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>53496; 83106</t>
+          <t>54446; 83524</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>93124; 133508</t>
+          <t>93518; 132755</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>72285; 108172</t>
+          <t>74142; 107463</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>56111; 224603</t>
+          <t>129479; 168669</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14136; 31206</t>
+          <t>12807; 30904</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21452; 42895</t>
+          <t>21962; 44703</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19564; 39665</t>
+          <t>19477; 42253</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>56135; 75731</t>
+          <t>62322; 83152</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>73368; 108157</t>
+          <t>73808; 108009</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>121465; 169319</t>
+          <t>121109; 166298</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>100339; 139288</t>
+          <t>99167; 139176</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>90331; 292084</t>
+          <t>198635; 243356</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>345683</t>
+          <t>378731</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>443947</t>
+          <t>260541</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>789629</t>
+          <t>639271</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>179743; 230559</t>
+          <t>179080; 232073</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>201305; 257694</t>
+          <t>201656; 255638</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>171870; 222817</t>
+          <t>171796; 221682</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>314864; 378911</t>
+          <t>347591; 410261</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>75621; 111944</t>
+          <t>75947; 112128</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>75929; 115640</t>
+          <t>76396; 113068</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>84632; 124049</t>
+          <t>85150; 127060</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>293659; 654919</t>
+          <t>237294; 282121</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>265418; 325594</t>
+          <t>267801; 331400</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>287949; 355920</t>
+          <t>289275; 353796</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>267315; 330557</t>
+          <t>268525; 328995</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>637342; 1154243</t>
+          <t>598967; 677706</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>128895</t>
+          <t>140443</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>266515</t>
+          <t>293509</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>395410</t>
+          <t>433952</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>38433; 64893</t>
+          <t>37874; 64066</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>77341; 111734</t>
+          <t>76318; 111443</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>96911; 135082</t>
+          <t>97138; 133687</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>109552; 147834</t>
+          <t>121131; 158636</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>63475; 99595</t>
+          <t>64850; 100626</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>128932; 173064</t>
+          <t>128338; 173647</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>103083; 145380</t>
+          <t>104702; 144877</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>199457; 305586</t>
+          <t>271866; 316159</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>110656; 156324</t>
+          <t>109479; 152088</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>218068; 272428</t>
+          <t>218458; 271827</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>210379; 265194</t>
+          <t>209178; 265864</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>307689; 433357</t>
+          <t>401221; 466687</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12981</t>
+          <t>11835</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>350434</t>
+          <t>379148</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>363415</t>
+          <t>390983</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6596; 20180</t>
+          <t>6058; 20107</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>14292; 33996</t>
+          <t>14174; 33720</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10398; 27109</t>
+          <t>9730; 28418</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6512; 26946</t>
+          <t>6387; 23067</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>247947; 305879</t>
+          <t>248072; 307026</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>275608; 337332</t>
+          <t>273008; 333552</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>243726; 304513</t>
+          <t>244205; 303664</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>327708; 374763</t>
+          <t>354254; 408414</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>259153; 319758</t>
+          <t>258408; 319322</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>292696; 356889</t>
+          <t>295358; 358785</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>260345; 322355</t>
+          <t>259790; 323907</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>329664; 391740</t>
+          <t>357047; 422008</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>982519</t>
+          <t>1067414</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1405692</t>
+          <t>1312609</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>2388211</t>
+          <t>2380024</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>417111; 493850</t>
+          <t>419404; 494639</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>560676; 646853</t>
+          <t>557927; 660902</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>495989; 577202</t>
+          <t>486302; 578068</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>781514; 1071862</t>
+          <t>1013109; 1121160</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>496309; 575906</t>
+          <t>494686; 577790</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>600878; 696172</t>
+          <t>598292; 698706</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>559667; 655704</t>
+          <t>564274; 660604</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1252539; 1879841</t>
+          <t>1265670; 1362545</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>933432; 1046199</t>
+          <t>932643; 1048885</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1182665; 1315438</t>
+          <t>1185327; 1318145</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1077897; 1205914</t>
+          <t>1082621; 1210355</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2149000; 2831238</t>
+          <t>2308095; 2452717</t>
         </is>
       </c>
     </row>
